--- a/asx_eod_output/Report_XLSX/Report_20251107.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20251107.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.015</v>
+        <v>1.012</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>155478.71</v>
+        <v>155019.17</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-4595.43</v>
+        <v>-5054.97</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.715</v>
+        <v>1.712</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-2.28%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>120050</v>
+        <v>119840</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-2800</v>
+        <v>-3010</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.71</v>
+        <v>0.705</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.045</v>
+        <v>-0.05</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>40795.18</v>
+        <v>40507.89</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2585.61</v>
+        <v>-2872.9</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>42.625</v>
+        <v>42.71</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.375</v>
+        <v>-0.29</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>16361</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>697387.62</v>
+        <v>698778.3100000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6135.37</v>
+        <v>-4744.69</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>176.8</v>
+        <v>177.14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-1.77</v>
+        <v>-1.43</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -785,14 +785,14 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>39.6</v>
+        <v>39.325</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -843,10 +843,10 @@
       <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="8" t="n">
-        <v>1063302.65</v>
+        <v>1063736.5</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>-15160.82</v>
+        <v>-14726.97</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20251107.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20251107.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.012</v>
+        <v>1.017</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.033</v>
+        <v>-0.028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>155019.17</v>
+        <v>155785.08</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-5054.97</v>
+        <v>-4289.07</v>
       </c>
     </row>
     <row r="5">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.705</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-6.62%</t>
+          <t>-8.61%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>40507.89</v>
+        <v>39646.02</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2872.9</v>
+        <v>-3734.77</v>
       </c>
     </row>
     <row r="7">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>177.14</v>
+        <v>177.17</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-1.43</v>
+        <v>-1.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -785,14 +785,14 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>39.325</v>
+        <v>39.205</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.385</v>
+        <v>-0.505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -812,24 +812,24 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>25.93</v>
+        <v>25.875</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.37</v>
+        <v>0.315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>33397.84</v>
+        <v>33327</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>476.56</v>
+        <v>405.72</v>
       </c>
     </row>
     <row r="17">
@@ -843,10 +843,10 @@
       <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="8" t="n">
-        <v>1063736.5</v>
+        <v>1063569.7</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>-14726.97</v>
+        <v>-14893.78</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20251107.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20251107.xlsx
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.712</v>
+        <v>1.705</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.043</v>
+        <v>-0.05</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>119840</v>
+        <v>119350</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-3010</v>
+        <v>-3500</v>
       </c>
     </row>
     <row r="6">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>177.17</v>
+        <v>177.19</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-1.4</v>
+        <v>-1.38</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -785,14 +785,14 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>39.205</v>
+        <v>39.19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.505</v>
+        <v>-0.52</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -812,24 +812,24 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>25.875</v>
+        <v>25.91</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.315</v>
+        <v>0.35</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>33327</v>
+        <v>33372.08</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>405.72</v>
+        <v>450.8</v>
       </c>
     </row>
     <row r="17">
@@ -843,10 +843,10 @@
       <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="8" t="n">
-        <v>1063569.7</v>
+        <v>1063124.78</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>-14893.78</v>
+        <v>-15338.7</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20251107.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20251107.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.017</v>
+        <v>1.01</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.028</v>
+        <v>-0.035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>155785.08</v>
+        <v>154712.81</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-4289.07</v>
+        <v>-5361.33</v>
       </c>
     </row>
     <row r="5">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.665</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.065</v>
+        <v>-0.09</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-8.61%</t>
+          <t>-11.92%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>39646.02</v>
+        <v>38209.57</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3734.77</v>
+        <v>-5171.22</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>42.71</v>
+        <v>42.65</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.35</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>16361</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>698778.3100000001</v>
+        <v>697796.65</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4744.69</v>
+        <v>-5726.35</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>177.19</v>
+        <v>175.91</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-1.38</v>
+        <v>-2.66</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.365</v>
+        <v>0.36</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3650</v>
+        <v>3600</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.295</v>
+        <v>0.29</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-4.92%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-200</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="12">
@@ -758,24 +758,24 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.245</v>
+        <v>0.235</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.003</v>
+        <v>-0.013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-5.24%</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>6000</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1470</v>
+        <v>1410</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-18</v>
+        <v>-78</v>
       </c>
     </row>
     <row r="15">
@@ -785,14 +785,14 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>39.19</v>
+        <v>38.98</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.73</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -812,24 +812,24 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>25.91</v>
+        <v>25.84</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>33372.08</v>
+        <v>33281.92</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>450.8</v>
+        <v>360.64</v>
       </c>
     </row>
     <row r="17">
@@ -843,10 +843,10 @@
       <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="8" t="n">
-        <v>1063124.78</v>
+        <v>1059334.24</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>-15338.7</v>
+        <v>-19129.23</v>
       </c>
     </row>
   </sheetData>
